--- a/assets/ejemplos excel ferreteria/1_catalogo_base_ferreteria.xlsx
+++ b/assets/ejemplos excel ferreteria/1_catalogo_base_ferreteria.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
+    <numFmt numFmtId="165" formatCode="0,##0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +34,25 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +63,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E293B"/>
         <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +121,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,761 +511,761 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Presentación</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Precio Unitario ($)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>ART-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Tornillos autoperforantes 1 pulgada</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Caja x 1000</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="8" t="n">
         <v>8500</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Tornillería</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>ART-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Tornillos tirafondo 1/4 x 2</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Caja x 100</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="11" t="n">
         <v>7200</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Tornillería</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>ART-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Tarugos con tope N°8</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Bolsa x 100</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="8" t="n">
         <v>3200</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Fijación</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>ART-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Disco de corte amoladora 115mm x 1mm</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="11" t="n">
         <v>1400</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Abrasivos</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>ART-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Disco de desbaste metal 115mm</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="8" t="n">
         <v>2800</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Abrasivos</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>ART-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Disco diamantado continuo 115mm</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="11" t="n">
         <v>6500</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Abrasivos</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>ART-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Amoladora angular 115mm 850W</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="8" t="n">
         <v>68000</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Herramientas Eléctricas</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>ART-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Taladro percutor 13mm 650W</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="11" t="n">
         <v>74000</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Herramientas Eléctricas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>ART-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Destornillador Phillips 6x100mm</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="8" t="n">
         <v>4800</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>ART-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Destornillador Plano 6x100mm</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="11" t="n">
         <v>4500</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ART-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Juego de destornilladores x 6 piezas</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="8" t="n">
         <v>18500</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ART-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Martillo galponero mango fibra 500g</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="11" t="n">
         <v>14500</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ART-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Pinza universal 8 pulgadas aislada</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="8" t="n">
         <v>12500</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ART-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Alicate corte diagonal 6 pulgadas</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="11" t="n">
         <v>11000</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>ART-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Llave francesa ajustable 10 pulgadas</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="8" t="n">
         <v>16500</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Herramientas Manuales</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>ART-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Cinta aisladora negra 20 metros</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Rollo</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="11" t="n">
         <v>1500</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Electricidad</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ART-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Cinta de teflón 3/4 x 20m</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Rollo</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="8" t="n">
         <v>950</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Plomería</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>ART-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Thinner estándar 1 litro</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Botella</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="11" t="n">
         <v>4200</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Pinturas &amp; Química</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ART-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Aguarrás mineral 1 litro</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Botella</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="8" t="n">
         <v>3800</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Pinturas &amp; Química</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>ART-020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Sellador de silicona neutra transparente 280ml</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Tubo</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="11" t="n">
         <v>6800</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Adhesivos &amp; Selladores</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>ART-021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Pegamento de contacto Poxiran 250cc</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Lata</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="8" t="n">
         <v>5400</v>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Adhesivos &amp; Selladores</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>ART-022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Candado de bronce 40mm con 3 llaves</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="11" t="n">
         <v>8900</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Cerrajería</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>ART-023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Pintura látex interior blanco 4L</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Balde</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="8" t="n">
         <v>22000</v>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Pinturas &amp; Química</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ART-024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Lija al agua grano 180</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Pliego</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="11" t="n">
         <v>650</v>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Abrasivos</t>
         </is>
